--- a/forms/trg/Formulir_TRG_neocare.xlsx
+++ b/forms/trg/Formulir_TRG_neocare.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Naoki Shimojo</t>
+          <t>Prof. dr. Andi Dwi Bahagia Febriani, Ph.D, Sp.A (K)</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Chiba University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Preventive Medicine</t>
+          <t>Neonatology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -950,22 +946,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. dr. Muh. Nasrum Massi, Ph.D., Sp.MK</t>
+          <t>Naoki Shimojo</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Chiba University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Preventive Medicine</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. dr. Ema Alasiry, Sp.A (K)</t>
+          <t>Prof. dr. Muh. Nasrum Massi, Ph.D., Sp.MK</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +998,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Neonatology</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1020,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>dr. Bahrul Fikri, Ph.D, Sp.A (K)</t>
+          <t>Dr. dr. Ema Alasiry, Sp.A (K)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1035,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Pediatrics, Allergy and Immunology</t>
+          <t>Neonatology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,12 +1057,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. dr. Martira Maddepungngeng, Sp.A(K)</t>
+          <t>dr. Bahrul Fikri, Ph.D, Sp.A (K)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>child development dan pediatric social</t>
+          <t>Pediatrics, Allergy and Immunology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,12 +1094,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. dr. Andi Alfian Zainuddin, M.K.M</t>
+          <t>Dr. dr. Martira Maddepungngeng, Sp.A(K)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1113,7 +1109,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Biostatistic</t>
+          <t>child development dan pediatric social</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,12 +1131,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Suni Hariati, Ners</t>
+          <t>Dr. dr. Andi Alfian Zainuddin, M.K.M</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1150,7 +1146,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Biostatistic</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1172,12 +1168,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>dr. Andi Yaumil Chaeriyah</t>
+          <t>Dr. Suni Hariati, Ners</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1187,7 +1183,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Research Assistant</t>
+          <t>Nursing</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,12 +1205,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>dr . Besse Sarmila, M.Kes, Sp.A (K)</t>
+          <t>dr. Andi Yaumil Chaeriyah</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1224,7 +1220,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Neonatology</t>
+          <t>Research Assistant</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,12 +1242,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>dr. Adhariana HK, M.Kes, Sp.A (K)</t>
+          <t>dr . Besse Sarmila, M.Kes, Sp.A (K)</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1281,10 +1277,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>dr. Adhariana HK, M.Kes, Sp.A (K)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Neonatology</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1292,7 +1304,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1481,15 +1497,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
